--- a/GATEWAY/A1#111#ESHARKSRLXX/e-Shark S.r.l/FaithK/2.9.17/report-checklist.xlsx
+++ b/GATEWAY/A1#111#ESHARKSRLXX/e-Shark S.r.l/FaithK/2.9.17/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\it-fse-accreditamento\GATEWAY\A1#111#ESHARKSRLXX\e-Shark S.r.l\FaithK\2.9.17\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323D5FE7-E383-4113-AB80-A94140538B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A53F3A-B530-4DDB-8422-65549CB509EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40785" yWindow="3780" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="449">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -1734,6 +1734,18 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.190.4.4.86368f3263265aed7dabc8472ec0934880333f568bd750456219b9f9570cabc5.4e7580eb6e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Timeout scaduto. È trascorso il periodo di timeout prima del completamento dell'operazione</t>
+  </si>
+  <si>
+    <t>Il medico clicca su "OK" sulla finestra di errore quindi può ritentare l'invio</t>
+  </si>
+  <si>
+    <t>Come da email del 13/01/2025 di Segreteria Tecnica FSE - Andrea Di Pietra con oggetto Oggetto: FSE 2.0 - Richiesta di sollecito accreditamento applicativi (cha ha superato il Test 0) , dove si specifica che "il superamento della fase 1 del processo di accreditamento è ritenuto valido se l’applicativo supera almeno il caso di test 1, tra quelli attualmente previsti per il Profilo Sanitario Sintetico sul sito di GitHub Test Case Profilo Sanitario Sintetico."</t>
+  </si>
+  <si>
+    <t>In base alle indicazioni contenute nella e-mail "PNRR M6C2 I1.3.1_DTD_FSE 2.0 - Processo di accreditamento (convalida) Profilo Sanitario Sintentico", questo caso di test non si applica per i software che non hanno ancora completato la procedura di accreditamento alla Fase 1, ma è riservato a quei software che hanno già superato questo accreditamento.</t>
   </si>
 </sst>
 </file>
@@ -4836,11 +4848,21 @@
       <c r="N29" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
+      <c r="O29" s="38" t="s">
+        <v>445</v>
+      </c>
+      <c r="P29" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q29" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="R29" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="S29" s="38" t="s">
+        <v>446</v>
+      </c>
       <c r="T29" s="38"/>
       <c r="U29" s="39" t="s">
         <v>64</v>
@@ -8617,8 +8639,12 @@
       <c r="G131" s="37"/>
       <c r="H131" s="37"/>
       <c r="I131" s="42"/>
-      <c r="J131" s="38"/>
-      <c r="K131" s="38"/>
+      <c r="J131" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K131" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L131" s="38"/>
       <c r="M131" s="38"/>
       <c r="N131" s="38"/>
@@ -8654,8 +8680,12 @@
       <c r="G132" s="37"/>
       <c r="H132" s="37"/>
       <c r="I132" s="42"/>
-      <c r="J132" s="38"/>
-      <c r="K132" s="38"/>
+      <c r="J132" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K132" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L132" s="38"/>
       <c r="M132" s="38"/>
       <c r="N132" s="38"/>
@@ -8691,8 +8721,12 @@
       <c r="G133" s="37"/>
       <c r="H133" s="37"/>
       <c r="I133" s="42"/>
-      <c r="J133" s="38"/>
-      <c r="K133" s="38"/>
+      <c r="J133" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K133" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L133" s="38"/>
       <c r="M133" s="38"/>
       <c r="N133" s="38"/>
@@ -8728,8 +8762,12 @@
       <c r="G134" s="37"/>
       <c r="H134" s="37"/>
       <c r="I134" s="42"/>
-      <c r="J134" s="38"/>
-      <c r="K134" s="38"/>
+      <c r="J134" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K134" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L134" s="38"/>
       <c r="M134" s="38"/>
       <c r="N134" s="38"/>
@@ -8765,8 +8803,12 @@
       <c r="G135" s="37"/>
       <c r="H135" s="37"/>
       <c r="I135" s="42"/>
-      <c r="J135" s="38"/>
-      <c r="K135" s="38"/>
+      <c r="J135" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K135" s="38" t="s">
+        <v>229</v>
+      </c>
       <c r="L135" s="38"/>
       <c r="M135" s="38"/>
       <c r="N135" s="38"/>
@@ -8802,8 +8844,12 @@
       <c r="G136" s="37"/>
       <c r="H136" s="37"/>
       <c r="I136" s="42"/>
-      <c r="J136" s="38"/>
-      <c r="K136" s="38"/>
+      <c r="J136" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K136" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L136" s="38"/>
       <c r="M136" s="38"/>
       <c r="N136" s="38"/>
@@ -8839,8 +8885,12 @@
       <c r="G137" s="37"/>
       <c r="H137" s="37"/>
       <c r="I137" s="42"/>
-      <c r="J137" s="38"/>
-      <c r="K137" s="38"/>
+      <c r="J137" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K137" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L137" s="38"/>
       <c r="M137" s="38"/>
       <c r="N137" s="38"/>
@@ -8876,8 +8926,12 @@
       <c r="G138" s="37"/>
       <c r="H138" s="37"/>
       <c r="I138" s="42"/>
-      <c r="J138" s="38"/>
-      <c r="K138" s="38"/>
+      <c r="J138" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K138" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L138" s="38"/>
       <c r="M138" s="38"/>
       <c r="N138" s="38"/>
@@ -8913,8 +8967,12 @@
       <c r="G139" s="37"/>
       <c r="H139" s="37"/>
       <c r="I139" s="42"/>
-      <c r="J139" s="38"/>
-      <c r="K139" s="38"/>
+      <c r="J139" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K139" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L139" s="38"/>
       <c r="M139" s="38"/>
       <c r="N139" s="38"/>
@@ -8950,8 +9008,12 @@
       <c r="G140" s="37"/>
       <c r="H140" s="37"/>
       <c r="I140" s="42"/>
-      <c r="J140" s="38"/>
-      <c r="K140" s="38"/>
+      <c r="J140" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K140" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L140" s="38"/>
       <c r="M140" s="38"/>
       <c r="N140" s="38"/>
@@ -8987,8 +9049,12 @@
       <c r="G141" s="37"/>
       <c r="H141" s="37"/>
       <c r="I141" s="42"/>
-      <c r="J141" s="38"/>
-      <c r="K141" s="38"/>
+      <c r="J141" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K141" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L141" s="38"/>
       <c r="M141" s="38"/>
       <c r="N141" s="38"/>
@@ -9024,8 +9090,12 @@
       <c r="G142" s="37"/>
       <c r="H142" s="37"/>
       <c r="I142" s="42"/>
-      <c r="J142" s="38"/>
-      <c r="K142" s="38"/>
+      <c r="J142" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K142" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L142" s="38"/>
       <c r="M142" s="38"/>
       <c r="N142" s="38"/>
@@ -9061,8 +9131,12 @@
       <c r="G143" s="37"/>
       <c r="H143" s="37"/>
       <c r="I143" s="42"/>
-      <c r="J143" s="38"/>
-      <c r="K143" s="38"/>
+      <c r="J143" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K143" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L143" s="38"/>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
@@ -9098,8 +9172,12 @@
       <c r="G144" s="37"/>
       <c r="H144" s="37"/>
       <c r="I144" s="42"/>
-      <c r="J144" s="38"/>
-      <c r="K144" s="38"/>
+      <c r="J144" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K144" s="38" t="s">
+        <v>234</v>
+      </c>
       <c r="L144" s="38"/>
       <c r="M144" s="38"/>
       <c r="N144" s="38"/>
@@ -9135,8 +9213,12 @@
       <c r="G145" s="37"/>
       <c r="H145" s="37"/>
       <c r="I145" s="42"/>
-      <c r="J145" s="38"/>
-      <c r="K145" s="38"/>
+      <c r="J145" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K145" s="38" t="s">
+        <v>231</v>
+      </c>
       <c r="L145" s="38"/>
       <c r="M145" s="38"/>
       <c r="N145" s="38"/>
@@ -10578,8 +10660,12 @@
       <c r="G184" s="35"/>
       <c r="H184" s="35"/>
       <c r="I184" s="35"/>
-      <c r="J184" s="38"/>
-      <c r="K184" s="38"/>
+      <c r="J184" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K184" s="38" t="s">
+        <v>231</v>
+      </c>
       <c r="L184" s="35"/>
       <c r="M184" s="38"/>
       <c r="N184" s="38"/>
@@ -10833,11 +10919,21 @@
       <c r="E191" s="43" t="s">
         <v>433</v>
       </c>
-      <c r="F191" s="37"/>
-      <c r="G191" s="37"/>
-      <c r="H191" s="37"/>
-      <c r="I191" s="42"/>
-      <c r="J191" s="38"/>
+      <c r="F191" s="37">
+        <v>46083</v>
+      </c>
+      <c r="G191" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="H191" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="I191" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="J191" s="38" t="s">
+        <v>64</v>
+      </c>
       <c r="K191" s="38"/>
       <c r="L191" s="38"/>
       <c r="M191" s="38"/>
@@ -10874,9 +10970,15 @@
       <c r="G192" s="37"/>
       <c r="H192" s="37"/>
       <c r="I192" s="42"/>
-      <c r="J192" s="38"/>
-      <c r="K192" s="38"/>
-      <c r="L192" s="38"/>
+      <c r="J192" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="K192" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="L192" s="38" t="s">
+        <v>447</v>
+      </c>
       <c r="M192" s="38"/>
       <c r="N192" s="38"/>
       <c r="O192" s="38"/>
@@ -10907,23 +11009,19 @@
       <c r="E193" s="45" t="s">
         <v>437</v>
       </c>
-      <c r="F193" s="37">
-        <v>46083</v>
-      </c>
-      <c r="G193" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="H193" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="I193" s="42" t="s">
-        <v>444</v>
-      </c>
+      <c r="F193" s="37"/>
+      <c r="G193" s="37"/>
+      <c r="H193" s="37"/>
+      <c r="I193" s="42"/>
       <c r="J193" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="K193" s="38"/>
-      <c r="L193" s="38"/>
+        <v>226</v>
+      </c>
+      <c r="K193" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="L193" s="38" t="s">
+        <v>448</v>
+      </c>
       <c r="M193" s="7"/>
       <c r="N193" s="38"/>
       <c r="O193" s="38"/>
@@ -17174,21 +17272,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17332,10 +17415,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17358,19 +17466,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
